--- a/src/modules/Masters/CustomerManagement/CustomerCreationretail/data/customer-creation.data.xlsx
+++ b/src/modules/Masters/CustomerManagement/CustomerCreationretail/data/customer-creation.data.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Create" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Auth" state="visible" r:id="rId5"/>
@@ -15,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>customerCategory</t>
   </si>
@@ -188,58 +191,88 @@
     <t>1</t>
   </si>
   <si>
+    <t>Harikrishan</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Enukonda</t>
+  </si>
+  <si>
+    <t>Sri</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Latha</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>01-01-1999</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ADKPH3443D</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>123 Test Street</t>
+  </si>
+  <si>
+    <t>Near Park</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>825301</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>test@example.com</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>TEST123</t>
+  </si>
+  <si>
+    <t>ISHAN SRI</t>
+  </si>
+  <si>
+    <t>searchKey</t>
+  </si>
+  <si>
+    <t>tab</t>
+  </si>
+  <si>
     <t>ISHAN</t>
   </si>
   <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>authorized</t>
+  </si>
+  <si>
     <t>SRI</t>
-  </si>
-  <si>
-    <t>01-01-1999</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>123 Test Street</t>
-  </si>
-  <si>
-    <t>Near Park</t>
-  </si>
-  <si>
-    <t>500001</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>test@example.com</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>TEST123</t>
-  </si>
-  <si>
-    <t>ISHAN SRI</t>
-  </si>
-  <si>
-    <t>searchKey</t>
-  </si>
-  <si>
-    <t>tab</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>authorized</t>
   </si>
   <si>
     <t>9876543211</t>
@@ -290,8 +323,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -314,10 +349,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -355,71 +390,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -443,50 +478,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -496,7 +534,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -505,7 +543,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -514,7 +552,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -522,10 +560,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -554,7 +592,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -567,13 +605,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -585,529 +622,483 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:BD2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="56" width="13.576428571428572" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="18.75" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" ht="18.75" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="J2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
-        <v>56</v>
-      </c>
-      <c r="R2" t="s">
-        <v>56</v>
-      </c>
-      <c r="S2" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" t="s">
-        <v>56</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="K2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
-        <v>57</v>
-      </c>
-      <c r="W2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="L2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC2" t="s">
+      <c r="M2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="N2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AE2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK2" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="V2" s="2">
+        <v>1</v>
+      </c>
+      <c r="W2" s="2">
+        <v>878277376755</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AN2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AX2" t="s">
+      <c r="Z2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AY2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AZ2" t="s">
+      <c r="AD2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BA2" t="s">
-        <v>57</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>57</v>
-      </c>
-      <c r="BC2" t="s">
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="AH2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="BD2" s="1" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="13.576428571428572" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" t="s">
-        <v>72</v>
+    <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
+    <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="8" width="13.576428571428572" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" t="s">
-        <v>76</v>
+    <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>77</v>
+    <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
+    <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>78</v>
+    <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>79</v>
+    <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/src/modules/Masters/CustomerManagement/CustomerCreationretail/data/customer-creation.data.xlsx
+++ b/src/modules/Masters/CustomerManagement/CustomerCreationretail/data/customer-creation.data.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Create" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Auth" state="visible" r:id="rId5"/>
@@ -18,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
   <si>
     <t>customerCategory</t>
   </si>
@@ -191,36 +188,21 @@
     <t>1</t>
   </si>
   <si>
-    <t>Harikrishan</t>
-  </si>
-  <si>
-    <t>Reddy</t>
-  </si>
-  <si>
-    <t>Enukonda</t>
-  </si>
-  <si>
-    <t>Sri</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Latha</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>ISHAN</t>
+  </si>
+  <si>
+    <t>SRI</t>
+  </si>
+  <si>
     <t>01-01-1999</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>ADKPH3443D</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -230,16 +212,7 @@
     <t>Near Park</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>825301</t>
+    <t>500001</t>
   </si>
   <si>
     <t>9876543210</t>
@@ -263,16 +236,10 @@
     <t>tab</t>
   </si>
   <si>
-    <t>ISHAN</t>
-  </si>
-  <si>
     <t>pending</t>
   </si>
   <si>
     <t>authorized</t>
-  </si>
-  <si>
-    <t>SRI</t>
   </si>
   <si>
     <t>9876543211</t>
@@ -323,10 +290,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -349,10 +314,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -390,71 +355,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -478,53 +443,50 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -534,7 +496,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -543,7 +505,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -552,7 +514,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -560,10 +522,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -592,7 +554,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -605,12 +567,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -622,483 +585,529 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:BD2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="56" width="13.576428571428572" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="V2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="Z2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC2" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="AD2" t="s">
         <v>64</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="AE2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="2">
-        <v>1</v>
-      </c>
-      <c r="W2" s="2">
-        <v>878277376755</v>
-      </c>
-      <c r="X2" s="1" t="s">
+      <c r="AL2" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AM2" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AN2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX2" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AY2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG2" s="1" t="s">
+      <c r="BA2" t="s">
+        <v>57</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>57</v>
+      </c>
+      <c r="BC2" t="s">
         <v>70</v>
       </c>
-      <c r="AH2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
-      <c r="AX2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY2" s="1"/>
-      <c r="AZ2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA2" s="1"/>
-      <c r="BB2" s="1"/>
-      <c r="BC2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BD2" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="13.576428571428572" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>82</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="8" width="13.576428571428572" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>86</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>87</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.576428571428572" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>89</v>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>